--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="46">
   <si>
     <t>event</t>
   </si>
@@ -142,6 +148,30 @@
   </si>
   <si>
     <t>engine(0-24), horn(12-60), shout(48-84), impact(72-240), shout(108-168)</t>
+  </si>
+  <si>
+    <t>shout(0-228), impact(132-156), impact(180-240)</t>
+  </si>
+  <si>
+    <t>shout(0-216), gunshot_or_explosion(120-144), impact(156-180), impact(204-240)</t>
+  </si>
+  <si>
+    <t>impact(0-144), shout(12-48), gunshot_or_explosion(108-132), tire_squeal(132-156), shout(144-192), impact(180-228), shout(216-240)</t>
+  </si>
+  <si>
+    <t>impact(0-144), impact(180-228), shout(12-48), shout(144-192), shout(216-240), gunshot_or_explosion(108-132), tire_squeal(132-156)</t>
+  </si>
+  <si>
+    <t>impact(0-24), shout(12-192), impact(72-144), engine(180-204), impact(192-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), horn(12-72), impact(60-240), gunshot_or_explosion(84-120), shout(120-144)</t>
+  </si>
+  <si>
+    <t>tire_squeal(0-24), shout(12-48), gunshot_or_explosion(36-60), impact(48-96), shout(84-132), impact(120-240), shout(156-216)</t>
+  </si>
+  <si>
+    <t>tire_squeal(0-24), shout(12-48), shout(84-132), shout(156-216), gunshot_or_explosion(36-60), impact(48-96), impact(120-240)</t>
   </si>
 </sst>
 </file>
@@ -969,6 +999,216 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -1006,6 +1246,145 @@
       </c>
       <c r="E2" t="s">
         <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -615,22 +615,22 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D4">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -641,22 +641,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -697,10 +697,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -846,10 +846,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -985,10 +985,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>

--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="45">
   <si>
     <t>event</t>
   </si>
@@ -102,25 +102,22 @@
     <t>shout(0-156), shout(204-240), gunshot_or_explosion(48-72), impact(108-216)</t>
   </si>
   <si>
-    <t>impact(0-36), shout(24-72), impact(60-96), gunshot_or_explosion(84-132), impact(120-216), gunshot_or_explosion(168-228), shout(216-240)</t>
-  </si>
-  <si>
-    <t>impact(0-36), impact(60-96), impact(120-216), shout(24-72), shout(216-240), gunshot_or_explosion(84-132), gunshot_or_explosion(168-228)</t>
-  </si>
-  <si>
-    <t>impact(0-60), shout(24-48), gunshot_or_explosion(48-84), shout(72-192), horn(180-204), impact(192-240)</t>
-  </si>
-  <si>
-    <t>impact(0-60), impact(192-240), shout(24-48), shout(72-192), gunshot_or_explosion(48-84), horn(180-204)</t>
-  </si>
-  <si>
-    <t>shout(0-24), impact(12-60), shout(48-240), gunshot_or_explosion(108-144), gunshot_or_explosion(192-216)</t>
+    <t>impact(0-216), shout(24-72), gunshot_or_explosion(84-132), gunshot_or_explosion(168-228), shout(216-240)</t>
+  </si>
+  <si>
+    <t>impact(0-60), shout(24-192), gunshot_or_explosion(48-84), horn(180-204), impact(192-240)</t>
+  </si>
+  <si>
+    <t>impact(0-60), impact(192-240), shout(24-192), gunshot_or_explosion(48-84), horn(180-204)</t>
+  </si>
+  <si>
+    <t>shout(0-240), impact(12-60), gunshot_or_explosion(108-144), gunshot_or_explosion(192-216)</t>
   </si>
   <si>
     <t>gunshot_or_explosion(0-36), impact(24-60), engine(48-96), shout(84-240), impact(120-144), engine(168-228), impact(180-204)</t>
   </si>
   <si>
-    <t>engine(0-24), impact(12-108), gunshot_or_explosion(24-48), shout(96-240), gunshot_or_explosion(120-144), impact(132-156)</t>
+    <t>engine(0-24), impact(12-156), gunshot_or_explosion(24-48), shout(96-240), gunshot_or_explosion(120-144)</t>
   </si>
   <si>
     <t>engine(0-24), impact(12-144), shout(132-192), tire_squeal(156-180), impact(180-240)</t>
@@ -129,16 +126,16 @@
     <t>shout(0-84), impact(72-96), engine(84-228), tire_squeal(180-216), impact(216-240)</t>
   </si>
   <si>
-    <t>shout(0-72), impact(36-108), engine(72-96), shout(96-132), engine(120-204), impact(144-168), shout(192-216), impact(204-240)</t>
-  </si>
-  <si>
-    <t>shout(0-72), shout(96-132), shout(192-216), impact(36-108), impact(144-168), impact(204-240), engine(72-96), engine(120-204)</t>
-  </si>
-  <si>
-    <t>horn(0-48), shout(36-84), impact(72-216), engine(84-120), gunshot_or_explosion(120-144), shout(156-180), shout(204-240)</t>
-  </si>
-  <si>
-    <t>horn(0-48), shout(36-84), shout(156-180), shout(204-240), impact(72-216), engine(84-120), gunshot_or_explosion(120-144)</t>
+    <t>shout(0-132), impact(36-108), engine(72-204), impact(144-168), shout(192-216), impact(204-240)</t>
+  </si>
+  <si>
+    <t>shout(0-132), shout(192-216), impact(36-108), impact(144-168), impact(204-240), engine(72-204)</t>
+  </si>
+  <si>
+    <t>horn(0-48), shout(36-84), impact(72-216), engine(84-120), gunshot_or_explosion(120-144), shout(156-240)</t>
+  </si>
+  <si>
+    <t>horn(0-48), shout(36-84), shout(156-240), impact(72-216), engine(84-120), gunshot_or_explosion(120-144)</t>
   </si>
   <si>
     <t>engine(0-24), impact(12-108), tire_squeal(24-48), shout(36-60), gunshot_or_explosion(96-132), shout(120-216), impact(204-240)</t>
@@ -147,19 +144,19 @@
     <t>engine(0-24), impact(12-108), impact(204-240), tire_squeal(24-48), shout(36-60), shout(120-216), gunshot_or_explosion(96-132)</t>
   </si>
   <si>
-    <t>engine(0-24), horn(12-60), shout(48-84), impact(72-240), shout(108-168)</t>
-  </si>
-  <si>
-    <t>shout(0-228), impact(132-156), impact(180-240)</t>
-  </si>
-  <si>
-    <t>shout(0-216), gunshot_or_explosion(120-144), impact(156-180), impact(204-240)</t>
-  </si>
-  <si>
-    <t>impact(0-144), shout(12-48), gunshot_or_explosion(108-132), tire_squeal(132-156), shout(144-192), impact(180-228), shout(216-240)</t>
-  </si>
-  <si>
-    <t>impact(0-144), impact(180-228), shout(12-48), shout(144-192), shout(216-240), gunshot_or_explosion(108-132), tire_squeal(132-156)</t>
+    <t>engine(0-24), horn(12-60), shout(48-168), impact(72-240)</t>
+  </si>
+  <si>
+    <t>shout(0-228), impact(132-240)</t>
+  </si>
+  <si>
+    <t>shout(0-216), gunshot_or_explosion(120-144), impact(156-240)</t>
+  </si>
+  <si>
+    <t>impact(0-144), shout(12-48), gunshot_or_explosion(108-132), tire_squeal(132-156), shout(144-240), impact(180-228)</t>
+  </si>
+  <si>
+    <t>impact(0-144), impact(180-228), shout(12-48), shout(144-240), gunshot_or_explosion(108-132), tire_squeal(132-156)</t>
   </si>
   <si>
     <t>impact(0-24), shout(12-192), impact(72-144), engine(180-204), impact(192-240)</t>
@@ -168,10 +165,10 @@
     <t>engine(0-24), horn(12-72), impact(60-240), gunshot_or_explosion(84-120), shout(120-144)</t>
   </si>
   <si>
-    <t>tire_squeal(0-24), shout(12-48), gunshot_or_explosion(36-60), impact(48-96), shout(84-132), impact(120-240), shout(156-216)</t>
-  </si>
-  <si>
-    <t>tire_squeal(0-24), shout(12-48), shout(84-132), shout(156-216), gunshot_or_explosion(36-60), impact(48-96), impact(120-240)</t>
+    <t>tire_squeal(0-24), shout(12-48), gunshot_or_explosion(36-60), impact(48-240), shout(84-216)</t>
+  </si>
+  <si>
+    <t>tire_squeal(0-24), shout(12-48), shout(84-216), gunshot_or_explosion(36-60), impact(48-240)</t>
   </si>
 </sst>
 </file>
@@ -575,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -703,6 +700,50 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -711,87 +752,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>13</v>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -808,51 +805,51 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -869,51 +866,51 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -930,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -947,6 +944,50 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -955,7 +996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -979,10 +1020,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -999,31 +1040,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1036,50 +1077,6 @@
       </c>
       <c r="E2" t="s">
         <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1096,51 +1093,51 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1157,6 +1154,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1165,7 +1206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1189,10 +1230,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -1201,95 +1242,51 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1306,51 +1303,51 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1358,7 +1355,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1367,24 +1364,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1516,6 +1496,50 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1538,7 +1562,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1550,68 +1574,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
         <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1628,6 +1591,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1636,7 +1643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1660,8 +1667,52 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>11</v>
+      </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1672,98 +1723,10 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>